--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEC45A3-3FD4-48A6-AAA8-60F56DB6B7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4283336-3EBD-446E-9D78-5376AA35A441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="1660" windowWidth="24990" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10910" yWindow="2070" windowWidth="24990" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,23 +54,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData#sep=+</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Remark</t>
   </si>
   <si>
@@ -81,26 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DollCatalog+100001Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DollCatalog+100001Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ImageName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">string </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品图片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ulockImageName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -113,11 +76,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>100001Image.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>100001MaskImage.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品表ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -446,18 +413,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="18.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.9140625" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="2" max="3" width="8.6640625" style="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +429,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>7</v>
@@ -473,14 +437,8 @@
       <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -488,22 +446,16 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -511,39 +463,27 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>24</v>
+      <c r="C4" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -1,122 +1,618 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4283336-3EBD-446E-9D78-5376AA35A441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10910" yWindow="2070" windowWidth="24990" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>ulockImageName</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>唯一ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Remark</t>
+  </si>
+  <si>
+    <t>物品表ID</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>娃娃一号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ulockImageName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>未解锁状态图片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100001MaskImage.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品表ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>少年剑士</t>
+  </si>
+  <si>
+    <t>魔法少女</t>
+  </si>
+  <si>
+    <t>日常校服少女</t>
+  </si>
+  <si>
+    <t>棒球少年</t>
+  </si>
+  <si>
+    <t>电竞少年</t>
+  </si>
+  <si>
+    <t>居家少女</t>
+  </si>
+  <si>
+    <t>骑士侍从</t>
+  </si>
+  <si>
+    <t>见习法师</t>
+  </si>
+  <si>
+    <t>短跑运动员</t>
+  </si>
+  <si>
+    <t>露营少年</t>
+  </si>
+  <si>
+    <t>水手少女</t>
+  </si>
+  <si>
+    <t>机车少年</t>
+  </si>
+  <si>
+    <t>花店少女</t>
+  </si>
+  <si>
+    <t>面包师少年</t>
+  </si>
+  <si>
+    <t>图书馆少女</t>
+  </si>
+  <si>
+    <t>滑板少年</t>
+  </si>
+  <si>
+    <t>茶艺少女</t>
+  </si>
+  <si>
+    <t>汽修少年</t>
+  </si>
+  <si>
+    <t>摄影少女</t>
+  </si>
+  <si>
+    <t>骑行少年</t>
+  </si>
+  <si>
+    <t>暗夜忍者</t>
+  </si>
+  <si>
+    <t>圣辉修女</t>
+  </si>
+  <si>
+    <t>龙纹武士</t>
+  </si>
+  <si>
+    <t>星海歌姬</t>
+  </si>
+  <si>
+    <t>白虎猎手</t>
+  </si>
+  <si>
+    <t>狐妖巫女</t>
+  </si>
+  <si>
+    <t>重装卫士</t>
+  </si>
+  <si>
+    <t>月影刺客</t>
+  </si>
+  <si>
+    <t>蔷薇骑士</t>
+  </si>
+  <si>
+    <t>极光魔法师</t>
+  </si>
+  <si>
+    <t>耀光剑士</t>
+  </si>
+  <si>
+    <t>星落歌姬</t>
+  </si>
+  <si>
+    <t>绯夜忍者</t>
+  </si>
+  <si>
+    <t>鎏金龙武士</t>
+  </si>
+  <si>
+    <t>极昼修女</t>
+  </si>
+  <si>
+    <t>苍雷猎手</t>
+  </si>
+  <si>
+    <t>幻梦狐妖</t>
+  </si>
+  <si>
+    <t>破晓骑士</t>
+  </si>
+  <si>
+    <t>永夜法师</t>
+  </si>
+  <si>
+    <t>星痕卫士</t>
+  </si>
+  <si>
+    <t>徽章</t>
+  </si>
+  <si>
+    <t>画册</t>
+  </si>
+  <si>
+    <t>抱枕</t>
+  </si>
+  <si>
+    <t>毯子</t>
+  </si>
+  <si>
+    <t>立牌</t>
+  </si>
+  <si>
+    <t>明信片</t>
+  </si>
+  <si>
+    <t>帆布包</t>
+  </si>
+  <si>
+    <t>文件夹</t>
+  </si>
+  <si>
+    <t>挂轴</t>
+  </si>
+  <si>
+    <t>海报</t>
+  </si>
+  <si>
+    <t>镭射票</t>
+  </si>
+  <si>
+    <t>手机壳</t>
+  </si>
+  <si>
+    <t>贴纸</t>
+  </si>
+  <si>
+    <t>本子</t>
+  </si>
+  <si>
+    <t>钥匙扣</t>
+  </si>
+  <si>
+    <t>T-恤</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -124,27 +620,340 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -193,7 +1002,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -228,7 +1037,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -402,92 +1211,789 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="3" width="8.66666666666667" style="2"/>
+    <col min="4" max="4" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="2">
+        <v>100001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" ref="E4:E59" si="0">CONCATENATE(B4,"MaskImage.png")</f>
+        <v>100001MaskImage.png</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="2">
+        <f t="shared" ref="B5:B43" si="1">B4+1</f>
+        <v>100002</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100002MaskImage.png</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="2">
+        <f t="shared" si="1"/>
+        <v>100003</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C4" s="1">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100003MaskImage.png</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="2">
+        <f t="shared" si="1"/>
+        <v>100004</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100004MaskImage.png</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="2">
+        <f t="shared" si="1"/>
+        <v>100005</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100005MaskImage.png</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="2">
+        <f t="shared" si="1"/>
+        <v>100006</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100006MaskImage.png</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="2">
+        <f t="shared" si="1"/>
+        <v>100007</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100007MaskImage.png</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="2">
+        <f t="shared" si="1"/>
+        <v>100008</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100008MaskImage.png</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="2">
+        <f t="shared" si="1"/>
+        <v>100009</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100009MaskImage.png</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="2">
+        <f t="shared" si="1"/>
+        <v>100010</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100010MaskImage.png</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="2">
+        <f t="shared" si="1"/>
+        <v>100011</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100011MaskImage.png</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="2">
+        <f t="shared" si="1"/>
+        <v>100012</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100012MaskImage.png</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="2">
+        <f t="shared" si="1"/>
+        <v>100013</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100013MaskImage.png</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2">
+        <f t="shared" si="1"/>
+        <v>100014</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100014MaskImage.png</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="2">
+        <f t="shared" si="1"/>
+        <v>100015</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100015MaskImage.png</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="2">
+        <f t="shared" si="1"/>
+        <v>100016</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100016MaskImage.png</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="2">
+        <f t="shared" si="1"/>
+        <v>100017</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100017MaskImage.png</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="2">
+        <f t="shared" si="1"/>
+        <v>100018</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100018MaskImage.png</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="2">
+        <f t="shared" si="1"/>
+        <v>100019</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100019MaskImage.png</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2">
+        <f t="shared" si="1"/>
+        <v>100020</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100020MaskImage.png</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>100021</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100021MaskImage.png</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2">
+        <f t="shared" si="1"/>
+        <v>100022</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100022MaskImage.png</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2">
+        <f t="shared" si="1"/>
+        <v>100023</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100023MaskImage.png</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="2">
+        <f t="shared" si="1"/>
+        <v>100024</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100024MaskImage.png</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="2">
+        <f t="shared" si="1"/>
+        <v>100025</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100025MaskImage.png</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="2">
+        <f t="shared" si="1"/>
+        <v>100026</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100026MaskImage.png</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="2">
+        <f t="shared" si="1"/>
+        <v>100027</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100027MaskImage.png</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="2">
+        <f t="shared" si="1"/>
+        <v>100028</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100028MaskImage.png</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="2">
+        <f t="shared" si="1"/>
+        <v>100029</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100029MaskImage.png</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="2">
+        <f t="shared" si="1"/>
+        <v>100030</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100030MaskImage.png</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="2">
+        <f t="shared" si="1"/>
+        <v>100031</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100031MaskImage.png</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="2">
+        <f t="shared" si="1"/>
+        <v>100032</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100032MaskImage.png</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="2">
+        <f t="shared" si="1"/>
+        <v>100033</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100033MaskImage.png</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="2">
+        <f t="shared" si="1"/>
+        <v>100034</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100034MaskImage.png</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="2">
+        <f t="shared" si="1"/>
+        <v>100035</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100035MaskImage.png</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="2">
+        <f t="shared" si="1"/>
+        <v>100036</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100036MaskImage.png</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="2">
+        <f t="shared" si="1"/>
+        <v>100037</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100037MaskImage.png</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="2">
+        <f t="shared" si="1"/>
+        <v>100038</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100038MaskImage.png</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="2">
+        <f t="shared" si="1"/>
+        <v>100039</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100039MaskImage.png</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="2">
+        <f t="shared" si="1"/>
+        <v>100040</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>100040MaskImage.png</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="2">
+        <v>210000</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210000MaskImage.png</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="2">
+        <v>210001</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210001MaskImage.png</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="2">
+        <v>210002</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210002MaskImage.png</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="2">
+        <v>210003</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210003MaskImage.png</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="2">
+        <v>210004</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210004MaskImage.png</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="2">
+        <v>210005</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210005MaskImage.png</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="2">
+        <v>210006</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210006MaskImage.png</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="2">
+        <v>210007</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210007MaskImage.png</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="2">
+        <v>210008</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210008MaskImage.png</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="2">
+        <v>210009</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210009MaskImage.png</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="2">
+        <v>210010</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210010MaskImage.png</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="2">
+        <v>210011</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210011MaskImage.png</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="2">
+        <v>210012</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210012MaskImage.png</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="2">
+        <v>210013</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210013MaskImage.png</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="2">
+        <v>210014</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210014MaskImage.png</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="2">
+        <v>210015</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>210015MaskImage.png</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754895F7-8F99-4102-BBED-1E05130752DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="1660" windowWidth="24990" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +44,12 @@
     <t>ulockImageName</t>
   </si>
   <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -59,6 +59,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -74,9 +77,18 @@
     <t>未解锁状态图片</t>
   </si>
   <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>预制体路径</t>
+  </si>
+  <si>
     <t>少年剑士</t>
   </si>
   <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Doll/Doll_100001.prefab</t>
+  </si>
+  <si>
     <t>魔法少女</t>
   </si>
   <si>
@@ -240,40 +252,19 @@
   </si>
   <si>
     <t>T-恤</t>
-  </si>
-  <si>
-    <t>Weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>权重</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PrefabPath</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>预制体路径</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/Doll/Doll_100001.prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,15 +276,160 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,8 +442,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -330,33 +652,322 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -614,25 +1225,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.66666666666667" style="1"/>
+    <col min="4" max="4" width="18.1666666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.4140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="80.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.4166666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="80.5833333333333" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,1114 +1256,1279 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" s="1">
         <v>100001</v>
       </c>
-      <c r="C4" s="1">
-        <v>100000</v>
+      <c r="C4" s="3">
+        <v>310000</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="str">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="str">
         <f t="shared" ref="E4:E59" si="0">CONCATENATE(B4,"MaskImage.png")</f>
         <v>100001MaskImage.png</v>
       </c>
-      <c r="F4" s="3">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="1">
         <f t="shared" ref="B5:B43" si="1">B4+1</f>
         <v>100002</v>
       </c>
+      <c r="C5" s="3">
+        <v>310001</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="str">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100002MaskImage.png</v>
       </c>
-      <c r="F5" s="3">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F5" s="2">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="1">
         <f t="shared" si="1"/>
         <v>100003</v>
       </c>
+      <c r="C6" s="3">
+        <v>310002</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3" t="str">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100003MaskImage.png</v>
       </c>
-      <c r="F6" s="3">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>100004</v>
       </c>
+      <c r="C7" s="3">
+        <v>310003</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="str">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100004MaskImage.png</v>
       </c>
-      <c r="F7" s="3">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>100005</v>
       </c>
+      <c r="C8" s="3">
+        <v>310004</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="3" t="str">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100005MaskImage.png</v>
       </c>
-      <c r="F8" s="3">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>100006</v>
       </c>
+      <c r="C9" s="3">
+        <v>310005</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="3" t="str">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100006MaskImage.png</v>
       </c>
-      <c r="F9" s="3">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>100007</v>
       </c>
+      <c r="C10" s="3">
+        <v>310006</v>
+      </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="str">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100007MaskImage.png</v>
       </c>
-      <c r="F10" s="3">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="2">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>100008</v>
       </c>
+      <c r="C11" s="3">
+        <v>310007</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="3" t="str">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100008MaskImage.png</v>
       </c>
-      <c r="F11" s="3">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>100009</v>
       </c>
+      <c r="C12" s="3">
+        <v>310008</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="3" t="str">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100009MaskImage.png</v>
       </c>
-      <c r="F12" s="3">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>100010</v>
       </c>
+      <c r="C13" s="3">
+        <v>310009</v>
+      </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="3" t="str">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100010MaskImage.png</v>
       </c>
-      <c r="F13" s="3">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="B14" s="1">
         <f t="shared" si="1"/>
         <v>100011</v>
       </c>
+      <c r="C14" s="3">
+        <v>310010</v>
+      </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="3" t="str">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100011MaskImage.png</v>
       </c>
-      <c r="F14" s="3">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="B15" s="1">
         <f t="shared" si="1"/>
         <v>100012</v>
       </c>
+      <c r="C15" s="3">
+        <v>310011</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="3" t="str">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100012MaskImage.png</v>
       </c>
-      <c r="F15" s="3">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="B16" s="1">
         <f t="shared" si="1"/>
         <v>100013</v>
       </c>
+      <c r="C16" s="3">
+        <v>310012</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3" t="str">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100013MaskImage.png</v>
       </c>
-      <c r="F16" s="3">
-        <v>10</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="2">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" s="1">
         <f t="shared" si="1"/>
         <v>100014</v>
       </c>
+      <c r="C17" s="3">
+        <v>310013</v>
+      </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="3" t="str">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100014MaskImage.png</v>
       </c>
-      <c r="F17" s="3">
-        <v>10</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="2">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" s="1">
         <f t="shared" si="1"/>
         <v>100015</v>
       </c>
+      <c r="C18" s="3">
+        <v>310014</v>
+      </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="3" t="str">
+        <v>33</v>
+      </c>
+      <c r="E18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100015MaskImage.png</v>
       </c>
-      <c r="F18" s="3">
-        <v>10</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F18" s="2">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" s="1">
         <f t="shared" si="1"/>
         <v>100016</v>
       </c>
+      <c r="C19" s="3">
+        <v>310015</v>
+      </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="3" t="str">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100016MaskImage.png</v>
       </c>
-      <c r="F19" s="3">
-        <v>10</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F19" s="2">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" s="1">
         <f t="shared" si="1"/>
         <v>100017</v>
       </c>
+      <c r="C20" s="3">
+        <v>310016</v>
+      </c>
       <c r="D20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="3" t="str">
+        <v>35</v>
+      </c>
+      <c r="E20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100017MaskImage.png</v>
       </c>
-      <c r="F20" s="3">
-        <v>10</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F20" s="2">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21" s="1">
         <f t="shared" si="1"/>
         <v>100018</v>
       </c>
+      <c r="C21" s="3">
+        <v>310017</v>
+      </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="3" t="str">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100018MaskImage.png</v>
       </c>
-      <c r="F21" s="3">
-        <v>10</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F21" s="2">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" s="1">
         <f t="shared" si="1"/>
         <v>100019</v>
       </c>
+      <c r="C22" s="3">
+        <v>310018</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="3" t="str">
+        <v>37</v>
+      </c>
+      <c r="E22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100019MaskImage.png</v>
       </c>
-      <c r="F22" s="3">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F22" s="2">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="1">
         <f t="shared" si="1"/>
         <v>100020</v>
       </c>
+      <c r="C23" s="3">
+        <v>310019</v>
+      </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="3" t="str">
+        <v>38</v>
+      </c>
+      <c r="E23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100020MaskImage.png</v>
       </c>
-      <c r="F23" s="3">
-        <v>10</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" s="1">
         <f t="shared" si="1"/>
         <v>100021</v>
       </c>
+      <c r="C24" s="3">
+        <v>310020</v>
+      </c>
       <c r="D24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="3" t="str">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100021MaskImage.png</v>
       </c>
-      <c r="F24" s="3">
-        <v>10</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F24" s="2">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" s="1">
         <f t="shared" si="1"/>
         <v>100022</v>
       </c>
+      <c r="C25" s="3">
+        <v>310021</v>
+      </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="3" t="str">
+        <v>40</v>
+      </c>
+      <c r="E25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100022MaskImage.png</v>
       </c>
-      <c r="F25" s="3">
-        <v>10</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26" s="1">
         <f t="shared" si="1"/>
         <v>100023</v>
       </c>
+      <c r="C26" s="3">
+        <v>310022</v>
+      </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="3" t="str">
+        <v>41</v>
+      </c>
+      <c r="E26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100023MaskImage.png</v>
       </c>
-      <c r="F26" s="3">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
       <c r="B27" s="1">
         <f t="shared" si="1"/>
         <v>100024</v>
       </c>
+      <c r="C27" s="3">
+        <v>310023</v>
+      </c>
       <c r="D27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="3" t="str">
+        <v>42</v>
+      </c>
+      <c r="E27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100024MaskImage.png</v>
       </c>
-      <c r="F27" s="3">
-        <v>10</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
       <c r="B28" s="1">
         <f t="shared" si="1"/>
         <v>100025</v>
       </c>
+      <c r="C28" s="3">
+        <v>310024</v>
+      </c>
       <c r="D28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="3" t="str">
+        <v>43</v>
+      </c>
+      <c r="E28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100025MaskImage.png</v>
       </c>
-      <c r="F28" s="3">
-        <v>10</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
       <c r="B29" s="1">
         <f t="shared" si="1"/>
         <v>100026</v>
       </c>
+      <c r="C29" s="3">
+        <v>310025</v>
+      </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="3" t="str">
+        <v>44</v>
+      </c>
+      <c r="E29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100026MaskImage.png</v>
       </c>
-      <c r="F29" s="3">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F29" s="2">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
       <c r="B30" s="1">
         <f t="shared" si="1"/>
         <v>100027</v>
       </c>
+      <c r="C30" s="3">
+        <v>310026</v>
+      </c>
       <c r="D30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="3" t="str">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100027MaskImage.png</v>
       </c>
-      <c r="F30" s="3">
-        <v>10</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F30" s="2">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31" s="1">
         <f t="shared" si="1"/>
         <v>100028</v>
       </c>
+      <c r="C31" s="3">
+        <v>310027</v>
+      </c>
       <c r="D31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="3" t="str">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100028MaskImage.png</v>
       </c>
-      <c r="F31" s="3">
-        <v>10</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
       <c r="B32" s="1">
         <f t="shared" si="1"/>
         <v>100029</v>
       </c>
+      <c r="C32" s="3">
+        <v>310028</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="3" t="str">
+        <v>47</v>
+      </c>
+      <c r="E32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100029MaskImage.png</v>
       </c>
-      <c r="F32" s="3">
-        <v>10</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F32" s="2">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
       <c r="B33" s="1">
         <f t="shared" si="1"/>
         <v>100030</v>
       </c>
+      <c r="C33" s="3">
+        <v>310029</v>
+      </c>
       <c r="D33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="3" t="str">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100030MaskImage.png</v>
       </c>
-      <c r="F33" s="3">
-        <v>10</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F33" s="2">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
       <c r="B34" s="1">
         <f t="shared" si="1"/>
         <v>100031</v>
       </c>
+      <c r="C34" s="3">
+        <v>310030</v>
+      </c>
       <c r="D34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="3" t="str">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100031MaskImage.png</v>
       </c>
-      <c r="F34" s="3">
-        <v>10</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="1">
         <f t="shared" si="1"/>
         <v>100032</v>
       </c>
+      <c r="C35" s="3">
+        <v>310031</v>
+      </c>
       <c r="D35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="3" t="str">
+        <v>50</v>
+      </c>
+      <c r="E35" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100032MaskImage.png</v>
       </c>
-      <c r="F35" s="3">
-        <v>10</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F35" s="2">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="1">
         <f t="shared" si="1"/>
         <v>100033</v>
       </c>
+      <c r="C36" s="3">
+        <v>310032</v>
+      </c>
       <c r="D36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="3" t="str">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100033MaskImage.png</v>
       </c>
-      <c r="F36" s="3">
-        <v>10</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F36" s="2">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37" s="1">
         <f t="shared" si="1"/>
         <v>100034</v>
       </c>
+      <c r="C37" s="3">
+        <v>310033</v>
+      </c>
       <c r="D37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E37" s="3" t="str">
+        <v>52</v>
+      </c>
+      <c r="E37" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100034MaskImage.png</v>
       </c>
-      <c r="F37" s="3">
-        <v>10</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="2">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" s="1">
         <f t="shared" si="1"/>
         <v>100035</v>
       </c>
+      <c r="C38" s="3">
+        <v>310034</v>
+      </c>
       <c r="D38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="3" t="str">
+        <v>53</v>
+      </c>
+      <c r="E38" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100035MaskImage.png</v>
       </c>
-      <c r="F38" s="3">
-        <v>10</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F38" s="2">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
       <c r="B39" s="1">
         <f t="shared" si="1"/>
         <v>100036</v>
       </c>
+      <c r="C39" s="3">
+        <v>310035</v>
+      </c>
       <c r="D39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="3" t="str">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100036MaskImage.png</v>
       </c>
-      <c r="F39" s="3">
-        <v>10</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F39" s="2">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
       <c r="B40" s="1">
         <f t="shared" si="1"/>
         <v>100037</v>
       </c>
+      <c r="C40" s="3">
+        <v>310036</v>
+      </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="3" t="str">
+        <v>55</v>
+      </c>
+      <c r="E40" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100037MaskImage.png</v>
       </c>
-      <c r="F40" s="3">
-        <v>10</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F40" s="2">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41" s="1">
         <f t="shared" si="1"/>
         <v>100038</v>
       </c>
+      <c r="C41" s="3">
+        <v>310037</v>
+      </c>
       <c r="D41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="3" t="str">
+        <v>56</v>
+      </c>
+      <c r="E41" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100038MaskImage.png</v>
       </c>
-      <c r="F41" s="3">
-        <v>10</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42" s="1">
         <f t="shared" si="1"/>
         <v>100039</v>
       </c>
+      <c r="C42" s="3">
+        <v>310038</v>
+      </c>
       <c r="D42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="3" t="str">
+        <v>57</v>
+      </c>
+      <c r="E42" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100039MaskImage.png</v>
       </c>
-      <c r="F42" s="3">
-        <v>10</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43" s="1">
         <f t="shared" si="1"/>
         <v>100040</v>
       </c>
+      <c r="C43" s="3">
+        <v>310039</v>
+      </c>
       <c r="D43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="3" t="str">
+        <v>58</v>
+      </c>
+      <c r="E43" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100040MaskImage.png</v>
       </c>
-      <c r="F43" s="3">
-        <v>10</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="2">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44" s="1">
         <v>210000</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="3" t="str">
+      <c r="C44" s="3">
+        <v>210000</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210000MaskImage.png</v>
       </c>
-      <c r="F44" s="3">
-        <v>10</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="2">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" s="1">
         <v>210001</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="3" t="str">
+      <c r="C45" s="3">
+        <v>210001</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210001MaskImage.png</v>
       </c>
-      <c r="F45" s="3">
-        <v>10</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F45" s="2">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46" s="1">
         <v>210002</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="3" t="str">
+      <c r="C46" s="3">
+        <v>210002</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210002MaskImage.png</v>
       </c>
-      <c r="F46" s="3">
-        <v>10</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F46" s="2">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
       <c r="B47" s="1">
         <v>210003</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E47" s="3" t="str">
+      <c r="C47" s="3">
+        <v>210003</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210003MaskImage.png</v>
       </c>
-      <c r="F47" s="3">
-        <v>10</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F47" s="2">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
       <c r="B48" s="1">
         <v>210004</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="3" t="str">
+      <c r="C48" s="3">
+        <v>210004</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210004MaskImage.png</v>
       </c>
-      <c r="F48" s="3">
-        <v>10</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F48" s="2">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
       <c r="B49" s="1">
         <v>210005</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="3" t="str">
+      <c r="C49" s="3">
+        <v>210005</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210005MaskImage.png</v>
       </c>
-      <c r="F49" s="3">
-        <v>10</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F49" s="2">
+        <v>10</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
       <c r="B50" s="1">
         <v>210006</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="3" t="str">
+      <c r="C50" s="3">
+        <v>210006</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210006MaskImage.png</v>
       </c>
-      <c r="F50" s="3">
-        <v>10</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F50" s="2">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
       <c r="B51" s="1">
         <v>210007</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="3" t="str">
+      <c r="C51" s="3">
+        <v>210007</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210007MaskImage.png</v>
       </c>
-      <c r="F51" s="3">
-        <v>10</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F51" s="2">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
       <c r="B52" s="1">
         <v>210008</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="3" t="str">
+      <c r="C52" s="3">
+        <v>210008</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210008MaskImage.png</v>
       </c>
-      <c r="F52" s="3">
-        <v>10</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F52" s="2">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
       <c r="B53" s="1">
         <v>210009</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="3" t="str">
+      <c r="C53" s="3">
+        <v>210009</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210009MaskImage.png</v>
       </c>
-      <c r="F53" s="3">
-        <v>10</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F53" s="2">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
       <c r="B54" s="1">
         <v>210010</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="3" t="str">
+      <c r="C54" s="3">
+        <v>210010</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210010MaskImage.png</v>
       </c>
-      <c r="F54" s="3">
-        <v>10</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F54" s="2">
+        <v>10</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
       <c r="B55" s="1">
         <v>210011</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="3" t="str">
+      <c r="C55" s="3">
+        <v>210011</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210011MaskImage.png</v>
       </c>
-      <c r="F55" s="3">
-        <v>10</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F55" s="2">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
       <c r="B56" s="1">
         <v>210012</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="3" t="str">
+      <c r="C56" s="3">
+        <v>210012</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210012MaskImage.png</v>
       </c>
-      <c r="F56" s="3">
-        <v>10</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F56" s="2">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
       <c r="B57" s="1">
         <v>210013</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="3" t="str">
+      <c r="C57" s="3">
+        <v>210013</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210013MaskImage.png</v>
       </c>
-      <c r="F57" s="3">
-        <v>10</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F57" s="2">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
       <c r="B58" s="1">
         <v>210014</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="3" t="str">
+      <c r="C58" s="3">
+        <v>210014</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210014MaskImage.png</v>
       </c>
-      <c r="F58" s="3">
-        <v>10</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F58" s="2">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
       <c r="B59" s="1">
         <v>210015</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" s="3" t="str">
+      <c r="C59" s="3">
+        <v>210015</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2" t="str">
         <f t="shared" si="0"/>
         <v>210015MaskImage.png</v>
       </c>
-      <c r="F59" s="3">
-        <v>10</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>75</v>
+      <c r="F59" s="2">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E23143-CC87-4D70-8340-498A507CC309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A035EBC-6CE3-4471-A0B1-CBAD3063CF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="1660" windowWidth="24990" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -258,14 +258,6 @@
   </si>
   <si>
     <t>T-恤</t>
-  </si>
-  <si>
-    <t>ImageName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁状态图片</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -295,6 +287,8 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -628,20 +622,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="10.58203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="26" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.4140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="80.58203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="26" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.4140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="80.58203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,19 +649,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -684,16 +675,13 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -707,19 +695,16 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>100001</v>
       </c>
@@ -730,21 +715,17 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f>CONCATENATE(C4,"Name.png")</f>
-        <v>310000Name.png</v>
-      </c>
-      <c r="F4" s="2" t="str">
         <f>CONCATENATE(B4,"MaskImage.png")</f>
         <v>100001MaskImage.png</v>
       </c>
-      <c r="G4" s="2">
-        <v>10</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <f t="shared" ref="B5:B43" si="0">B4+1</f>
         <v>100002</v>
@@ -756,21 +737,17 @@
         <v>20</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f t="shared" ref="E5:E59" si="1">CONCATENATE(C5,"Name.png")</f>
-        <v>310001Name.png</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <f t="shared" ref="F5:F59" si="2">CONCATENATE(B5,"MaskImage.png")</f>
+        <f t="shared" ref="E5:E59" si="1">CONCATENATE(B5,"MaskImage.png")</f>
         <v>100002MaskImage.png</v>
       </c>
-      <c r="G5" s="2">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F5" s="2">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <f t="shared" si="0"/>
         <v>100003</v>
@@ -783,20 +760,16 @@
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310002Name.png</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100003MaskImage.png</v>
       </c>
-      <c r="G6" s="2">
-        <v>10</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <f t="shared" si="0"/>
         <v>100004</v>
@@ -809,20 +782,16 @@
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310003Name.png</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100004MaskImage.png</v>
       </c>
-      <c r="G7" s="2">
-        <v>10</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <f t="shared" si="0"/>
         <v>100005</v>
@@ -835,20 +804,16 @@
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310004Name.png</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100005MaskImage.png</v>
       </c>
-      <c r="G8" s="2">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <f t="shared" si="0"/>
         <v>100006</v>
@@ -861,20 +826,16 @@
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310005Name.png</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100006MaskImage.png</v>
       </c>
-      <c r="G9" s="2">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>100007</v>
@@ -887,20 +848,16 @@
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310006Name.png</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100007MaskImage.png</v>
       </c>
-      <c r="G10" s="2">
-        <v>10</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" s="2">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>100008</v>
@@ -913,20 +870,16 @@
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310007Name.png</v>
-      </c>
-      <c r="F11" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100008MaskImage.png</v>
       </c>
-      <c r="G11" s="2">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>100009</v>
@@ -939,20 +892,16 @@
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310008Name.png</v>
-      </c>
-      <c r="F12" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100009MaskImage.png</v>
       </c>
-      <c r="G12" s="2">
-        <v>10</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>100010</v>
@@ -965,20 +914,16 @@
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310009Name.png</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100010MaskImage.png</v>
       </c>
-      <c r="G13" s="2">
-        <v>10</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>100011</v>
@@ -991,20 +936,16 @@
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310010Name.png</v>
-      </c>
-      <c r="F14" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100011MaskImage.png</v>
       </c>
-      <c r="G14" s="2">
-        <v>10</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>100012</v>
@@ -1017,20 +958,16 @@
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310011Name.png</v>
-      </c>
-      <c r="F15" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100012MaskImage.png</v>
       </c>
-      <c r="G15" s="2">
-        <v>10</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>100013</v>
@@ -1043,20 +980,16 @@
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310012Name.png</v>
-      </c>
-      <c r="F16" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100013MaskImage.png</v>
       </c>
-      <c r="G16" s="2">
-        <v>10</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F16" s="2">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>100014</v>
@@ -1069,20 +1002,16 @@
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310013Name.png</v>
-      </c>
-      <c r="F17" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100014MaskImage.png</v>
       </c>
-      <c r="G17" s="2">
-        <v>10</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F17" s="2">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>100015</v>
@@ -1095,20 +1024,16 @@
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310014Name.png</v>
-      </c>
-      <c r="F18" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100015MaskImage.png</v>
       </c>
-      <c r="G18" s="2">
-        <v>10</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F18" s="2">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>100016</v>
@@ -1121,20 +1046,16 @@
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310015Name.png</v>
-      </c>
-      <c r="F19" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100016MaskImage.png</v>
       </c>
-      <c r="G19" s="2">
-        <v>10</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F19" s="2">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>100017</v>
@@ -1147,20 +1068,16 @@
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310016Name.png</v>
-      </c>
-      <c r="F20" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100017MaskImage.png</v>
       </c>
-      <c r="G20" s="2">
-        <v>10</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F20" s="2">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <f t="shared" si="0"/>
         <v>100018</v>
@@ -1173,20 +1090,16 @@
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310017Name.png</v>
-      </c>
-      <c r="F21" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100018MaskImage.png</v>
       </c>
-      <c r="G21" s="2">
-        <v>10</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F21" s="2">
+        <v>10</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>100019</v>
@@ -1199,20 +1112,16 @@
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310018Name.png</v>
-      </c>
-      <c r="F22" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100019MaskImage.png</v>
       </c>
-      <c r="G22" s="2">
-        <v>10</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F22" s="2">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>100020</v>
@@ -1225,20 +1134,16 @@
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310019Name.png</v>
-      </c>
-      <c r="F23" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100020MaskImage.png</v>
       </c>
-      <c r="G23" s="2">
-        <v>10</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>100021</v>
@@ -1251,20 +1156,16 @@
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310020Name.png</v>
-      </c>
-      <c r="F24" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100021MaskImage.png</v>
       </c>
-      <c r="G24" s="2">
-        <v>10</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F24" s="2">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>100022</v>
@@ -1277,20 +1178,16 @@
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310021Name.png</v>
-      </c>
-      <c r="F25" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100022MaskImage.png</v>
       </c>
-      <c r="G25" s="2">
-        <v>10</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <f t="shared" si="0"/>
         <v>100023</v>
@@ -1303,20 +1200,16 @@
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310022Name.png</v>
-      </c>
-      <c r="F26" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100023MaskImage.png</v>
       </c>
-      <c r="G26" s="2">
-        <v>10</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <f t="shared" si="0"/>
         <v>100024</v>
@@ -1329,20 +1222,16 @@
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310023Name.png</v>
-      </c>
-      <c r="F27" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100024MaskImage.png</v>
       </c>
-      <c r="G27" s="2">
-        <v>10</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>100025</v>
@@ -1355,20 +1244,16 @@
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310024Name.png</v>
-      </c>
-      <c r="F28" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100025MaskImage.png</v>
       </c>
-      <c r="G28" s="2">
-        <v>10</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <f t="shared" si="0"/>
         <v>100026</v>
@@ -1381,20 +1266,16 @@
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310025Name.png</v>
-      </c>
-      <c r="F29" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100026MaskImage.png</v>
       </c>
-      <c r="G29" s="2">
-        <v>10</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F29" s="2">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>100027</v>
@@ -1407,20 +1288,16 @@
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310026Name.png</v>
-      </c>
-      <c r="F30" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100027MaskImage.png</v>
       </c>
-      <c r="G30" s="2">
-        <v>10</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F30" s="2">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <f t="shared" si="0"/>
         <v>100028</v>
@@ -1433,20 +1310,16 @@
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310027Name.png</v>
-      </c>
-      <c r="F31" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100028MaskImage.png</v>
       </c>
-      <c r="G31" s="2">
-        <v>10</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <f t="shared" si="0"/>
         <v>100029</v>
@@ -1459,20 +1332,16 @@
       </c>
       <c r="E32" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310028Name.png</v>
-      </c>
-      <c r="F32" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100029MaskImage.png</v>
       </c>
-      <c r="G32" s="2">
-        <v>10</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F32" s="2">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <f t="shared" si="0"/>
         <v>100030</v>
@@ -1485,20 +1354,16 @@
       </c>
       <c r="E33" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310029Name.png</v>
-      </c>
-      <c r="F33" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100030MaskImage.png</v>
       </c>
-      <c r="G33" s="2">
-        <v>10</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F33" s="2">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>100031</v>
@@ -1511,20 +1376,16 @@
       </c>
       <c r="E34" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310030Name.png</v>
-      </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100031MaskImage.png</v>
       </c>
-      <c r="G34" s="2">
-        <v>10</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <f t="shared" si="0"/>
         <v>100032</v>
@@ -1537,20 +1398,16 @@
       </c>
       <c r="E35" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310031Name.png</v>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100032MaskImage.png</v>
       </c>
-      <c r="G35" s="2">
-        <v>10</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F35" s="2">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <f t="shared" si="0"/>
         <v>100033</v>
@@ -1563,20 +1420,16 @@
       </c>
       <c r="E36" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310032Name.png</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100033MaskImage.png</v>
       </c>
-      <c r="G36" s="2">
-        <v>10</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F36" s="2">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>100034</v>
@@ -1589,20 +1442,16 @@
       </c>
       <c r="E37" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310033Name.png</v>
-      </c>
-      <c r="F37" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100034MaskImage.png</v>
       </c>
-      <c r="G37" s="2">
-        <v>10</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F37" s="2">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>100035</v>
@@ -1615,20 +1464,16 @@
       </c>
       <c r="E38" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310034Name.png</v>
-      </c>
-      <c r="F38" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100035MaskImage.png</v>
       </c>
-      <c r="G38" s="2">
-        <v>10</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F38" s="2">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <f t="shared" si="0"/>
         <v>100036</v>
@@ -1641,20 +1486,16 @@
       </c>
       <c r="E39" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310035Name.png</v>
-      </c>
-      <c r="F39" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100036MaskImage.png</v>
       </c>
-      <c r="G39" s="2">
-        <v>10</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F39" s="2">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>100037</v>
@@ -1667,20 +1508,16 @@
       </c>
       <c r="E40" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310036Name.png</v>
-      </c>
-      <c r="F40" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100037MaskImage.png</v>
       </c>
-      <c r="G40" s="2">
-        <v>10</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F40" s="2">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <f t="shared" si="0"/>
         <v>100038</v>
@@ -1693,20 +1530,16 @@
       </c>
       <c r="E41" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310037Name.png</v>
-      </c>
-      <c r="F41" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100038MaskImage.png</v>
       </c>
-      <c r="G41" s="2">
-        <v>10</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <f t="shared" si="0"/>
         <v>100039</v>
@@ -1719,20 +1552,16 @@
       </c>
       <c r="E42" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310038Name.png</v>
-      </c>
-      <c r="F42" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100039MaskImage.png</v>
       </c>
-      <c r="G42" s="2">
-        <v>10</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>100040</v>
@@ -1745,20 +1574,16 @@
       </c>
       <c r="E43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>310039Name.png</v>
-      </c>
-      <c r="F43" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>100040MaskImage.png</v>
       </c>
-      <c r="G43" s="2">
-        <v>10</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F43" s="2">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>210000</v>
       </c>
@@ -1770,20 +1595,16 @@
       </c>
       <c r="E44" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210000Name.png</v>
-      </c>
-      <c r="F44" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210000MaskImage.png</v>
       </c>
-      <c r="G44" s="2">
-        <v>10</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F44" s="2">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>210001</v>
       </c>
@@ -1795,20 +1616,16 @@
       </c>
       <c r="E45" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210001Name.png</v>
-      </c>
-      <c r="F45" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210001MaskImage.png</v>
       </c>
-      <c r="G45" s="2">
-        <v>10</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F45" s="2">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>210002</v>
       </c>
@@ -1820,20 +1637,16 @@
       </c>
       <c r="E46" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210002Name.png</v>
-      </c>
-      <c r="F46" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210002MaskImage.png</v>
       </c>
-      <c r="G46" s="2">
-        <v>10</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F46" s="2">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>210003</v>
       </c>
@@ -1845,20 +1658,16 @@
       </c>
       <c r="E47" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210003Name.png</v>
-      </c>
-      <c r="F47" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210003MaskImage.png</v>
       </c>
-      <c r="G47" s="2">
-        <v>10</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F47" s="2">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>210004</v>
       </c>
@@ -1870,20 +1679,16 @@
       </c>
       <c r="E48" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210004Name.png</v>
-      </c>
-      <c r="F48" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210004MaskImage.png</v>
       </c>
-      <c r="G48" s="2">
-        <v>10</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F48" s="2">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>210005</v>
       </c>
@@ -1895,20 +1700,16 @@
       </c>
       <c r="E49" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210005Name.png</v>
-      </c>
-      <c r="F49" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210005MaskImage.png</v>
       </c>
-      <c r="G49" s="2">
-        <v>10</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F49" s="2">
+        <v>10</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>210006</v>
       </c>
@@ -1920,20 +1721,16 @@
       </c>
       <c r="E50" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210006Name.png</v>
-      </c>
-      <c r="F50" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210006MaskImage.png</v>
       </c>
-      <c r="G50" s="2">
-        <v>10</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F50" s="2">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>210007</v>
       </c>
@@ -1945,20 +1742,16 @@
       </c>
       <c r="E51" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210007Name.png</v>
-      </c>
-      <c r="F51" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210007MaskImage.png</v>
       </c>
-      <c r="G51" s="2">
-        <v>10</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F51" s="2">
+        <v>10</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>210008</v>
       </c>
@@ -1970,20 +1763,16 @@
       </c>
       <c r="E52" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210008Name.png</v>
-      </c>
-      <c r="F52" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210008MaskImage.png</v>
       </c>
-      <c r="G52" s="2">
-        <v>10</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F52" s="2">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>210009</v>
       </c>
@@ -1995,20 +1784,16 @@
       </c>
       <c r="E53" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210009Name.png</v>
-      </c>
-      <c r="F53" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210009MaskImage.png</v>
       </c>
-      <c r="G53" s="2">
-        <v>10</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F53" s="2">
+        <v>10</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>210010</v>
       </c>
@@ -2020,20 +1805,16 @@
       </c>
       <c r="E54" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210010Name.png</v>
-      </c>
-      <c r="F54" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210010MaskImage.png</v>
       </c>
-      <c r="G54" s="2">
-        <v>10</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F54" s="2">
+        <v>10</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>210011</v>
       </c>
@@ -2045,20 +1826,16 @@
       </c>
       <c r="E55" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210011Name.png</v>
-      </c>
-      <c r="F55" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210011MaskImage.png</v>
       </c>
-      <c r="G55" s="2">
-        <v>10</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F55" s="2">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>210012</v>
       </c>
@@ -2070,20 +1847,16 @@
       </c>
       <c r="E56" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210012Name.png</v>
-      </c>
-      <c r="F56" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210012MaskImage.png</v>
       </c>
-      <c r="G56" s="2">
-        <v>10</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F56" s="2">
+        <v>10</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>210013</v>
       </c>
@@ -2095,20 +1868,16 @@
       </c>
       <c r="E57" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210013Name.png</v>
-      </c>
-      <c r="F57" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210013MaskImage.png</v>
       </c>
-      <c r="G57" s="2">
-        <v>10</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F57" s="2">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>210014</v>
       </c>
@@ -2120,20 +1889,16 @@
       </c>
       <c r="E58" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210014Name.png</v>
-      </c>
-      <c r="F58" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210014MaskImage.png</v>
       </c>
-      <c r="G58" s="2">
-        <v>10</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F58" s="2">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>210015</v>
       </c>
@@ -2145,16 +1910,12 @@
       </c>
       <c r="E59" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>210015Name.png</v>
-      </c>
-      <c r="F59" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>210015MaskImage.png</v>
       </c>
-      <c r="G59" s="2">
-        <v>10</v>
-      </c>
-      <c r="H59" s="2" t="s">
+      <c r="F59" s="2">
+        <v>10</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>19</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A035EBC-6CE3-4471-A0B1-CBAD3063CF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA22A4D-B6ED-4572-84CD-DB7443E21BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4940" yWindow="2920" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -737,7 +737,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f t="shared" ref="E5:E59" si="1">CONCATENATE(B5,"MaskImage.png")</f>
+        <f>CONCATENATE(B5,"MaskImage.png")</f>
         <v>100002MaskImage.png</v>
       </c>
       <c r="F5" s="2">
@@ -759,7 +759,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B6,"MaskImage.png")</f>
         <v>100003MaskImage.png</v>
       </c>
       <c r="F6" s="2">
@@ -781,7 +781,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B7,"MaskImage.png")</f>
         <v>100004MaskImage.png</v>
       </c>
       <c r="F7" s="2">
@@ -803,7 +803,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B8,"MaskImage.png")</f>
         <v>100005MaskImage.png</v>
       </c>
       <c r="F8" s="2">
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B9,"MaskImage.png")</f>
         <v>100006MaskImage.png</v>
       </c>
       <c r="F9" s="2">
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B10,"MaskImage.png")</f>
         <v>100007MaskImage.png</v>
       </c>
       <c r="F10" s="2">
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B11,"MaskImage.png")</f>
         <v>100008MaskImage.png</v>
       </c>
       <c r="F11" s="2">
@@ -891,7 +891,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B12,"MaskImage.png")</f>
         <v>100009MaskImage.png</v>
       </c>
       <c r="F12" s="2">
@@ -913,7 +913,7 @@
         <v>28</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B13,"MaskImage.png")</f>
         <v>100010MaskImage.png</v>
       </c>
       <c r="F13" s="2">
@@ -935,7 +935,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B14,"MaskImage.png")</f>
         <v>100011MaskImage.png</v>
       </c>
       <c r="F14" s="2">
@@ -957,7 +957,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B15,"MaskImage.png")</f>
         <v>100012MaskImage.png</v>
       </c>
       <c r="F15" s="2">
@@ -979,7 +979,7 @@
         <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B16,"MaskImage.png")</f>
         <v>100013MaskImage.png</v>
       </c>
       <c r="F16" s="2">
@@ -1001,7 +1001,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B17,"MaskImage.png")</f>
         <v>100014MaskImage.png</v>
       </c>
       <c r="F17" s="2">
@@ -1023,7 +1023,7 @@
         <v>33</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B18,"MaskImage.png")</f>
         <v>100015MaskImage.png</v>
       </c>
       <c r="F18" s="2">
@@ -1045,7 +1045,7 @@
         <v>34</v>
       </c>
       <c r="E19" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B19,"MaskImage.png")</f>
         <v>100016MaskImage.png</v>
       </c>
       <c r="F19" s="2">
@@ -1067,7 +1067,7 @@
         <v>35</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B20,"MaskImage.png")</f>
         <v>100017MaskImage.png</v>
       </c>
       <c r="F20" s="2">
@@ -1089,7 +1089,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B21,"MaskImage.png")</f>
         <v>100018MaskImage.png</v>
       </c>
       <c r="F21" s="2">
@@ -1111,7 +1111,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B22,"MaskImage.png")</f>
         <v>100019MaskImage.png</v>
       </c>
       <c r="F22" s="2">
@@ -1133,7 +1133,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B23,"MaskImage.png")</f>
         <v>100020MaskImage.png</v>
       </c>
       <c r="F23" s="2">
@@ -1155,7 +1155,7 @@
         <v>39</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B24,"MaskImage.png")</f>
         <v>100021MaskImage.png</v>
       </c>
       <c r="F24" s="2">
@@ -1177,7 +1177,7 @@
         <v>40</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B25,"MaskImage.png")</f>
         <v>100022MaskImage.png</v>
       </c>
       <c r="F25" s="2">
@@ -1199,7 +1199,7 @@
         <v>41</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B26,"MaskImage.png")</f>
         <v>100023MaskImage.png</v>
       </c>
       <c r="F26" s="2">
@@ -1221,7 +1221,7 @@
         <v>42</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B27,"MaskImage.png")</f>
         <v>100024MaskImage.png</v>
       </c>
       <c r="F27" s="2">
@@ -1243,7 +1243,7 @@
         <v>43</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B28,"MaskImage.png")</f>
         <v>100025MaskImage.png</v>
       </c>
       <c r="F28" s="2">
@@ -1265,7 +1265,7 @@
         <v>44</v>
       </c>
       <c r="E29" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B29,"MaskImage.png")</f>
         <v>100026MaskImage.png</v>
       </c>
       <c r="F29" s="2">
@@ -1287,7 +1287,7 @@
         <v>45</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B30,"MaskImage.png")</f>
         <v>100027MaskImage.png</v>
       </c>
       <c r="F30" s="2">
@@ -1309,7 +1309,7 @@
         <v>46</v>
       </c>
       <c r="E31" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B31,"MaskImage.png")</f>
         <v>100028MaskImage.png</v>
       </c>
       <c r="F31" s="2">
@@ -1331,7 +1331,7 @@
         <v>47</v>
       </c>
       <c r="E32" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B32,"MaskImage.png")</f>
         <v>100029MaskImage.png</v>
       </c>
       <c r="F32" s="2">
@@ -1353,7 +1353,7 @@
         <v>48</v>
       </c>
       <c r="E33" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B33,"MaskImage.png")</f>
         <v>100030MaskImage.png</v>
       </c>
       <c r="F33" s="2">
@@ -1375,7 +1375,7 @@
         <v>49</v>
       </c>
       <c r="E34" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B34,"MaskImage.png")</f>
         <v>100031MaskImage.png</v>
       </c>
       <c r="F34" s="2">
@@ -1397,7 +1397,7 @@
         <v>50</v>
       </c>
       <c r="E35" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B35,"MaskImage.png")</f>
         <v>100032MaskImage.png</v>
       </c>
       <c r="F35" s="2">
@@ -1419,7 +1419,7 @@
         <v>51</v>
       </c>
       <c r="E36" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B36,"MaskImage.png")</f>
         <v>100033MaskImage.png</v>
       </c>
       <c r="F36" s="2">
@@ -1441,7 +1441,7 @@
         <v>52</v>
       </c>
       <c r="E37" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B37,"MaskImage.png")</f>
         <v>100034MaskImage.png</v>
       </c>
       <c r="F37" s="2">
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="E38" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B38,"MaskImage.png")</f>
         <v>100035MaskImage.png</v>
       </c>
       <c r="F38" s="2">
@@ -1485,7 +1485,7 @@
         <v>54</v>
       </c>
       <c r="E39" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B39,"MaskImage.png")</f>
         <v>100036MaskImage.png</v>
       </c>
       <c r="F39" s="2">
@@ -1507,7 +1507,7 @@
         <v>55</v>
       </c>
       <c r="E40" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B40,"MaskImage.png")</f>
         <v>100037MaskImage.png</v>
       </c>
       <c r="F40" s="2">
@@ -1529,7 +1529,7 @@
         <v>56</v>
       </c>
       <c r="E41" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B41,"MaskImage.png")</f>
         <v>100038MaskImage.png</v>
       </c>
       <c r="F41" s="2">
@@ -1551,7 +1551,7 @@
         <v>57</v>
       </c>
       <c r="E42" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B42,"MaskImage.png")</f>
         <v>100039MaskImage.png</v>
       </c>
       <c r="F42" s="2">
@@ -1573,7 +1573,7 @@
         <v>58</v>
       </c>
       <c r="E43" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B43,"MaskImage.png")</f>
         <v>100040MaskImage.png</v>
       </c>
       <c r="F43" s="2">
@@ -1594,7 +1594,7 @@
         <v>59</v>
       </c>
       <c r="E44" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B44,"MaskImage.png")</f>
         <v>210000MaskImage.png</v>
       </c>
       <c r="F44" s="2">
@@ -1615,7 +1615,7 @@
         <v>60</v>
       </c>
       <c r="E45" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B45,"MaskImage.png")</f>
         <v>210001MaskImage.png</v>
       </c>
       <c r="F45" s="2">
@@ -1636,7 +1636,7 @@
         <v>61</v>
       </c>
       <c r="E46" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B46,"MaskImage.png")</f>
         <v>210002MaskImage.png</v>
       </c>
       <c r="F46" s="2">
@@ -1657,7 +1657,7 @@
         <v>62</v>
       </c>
       <c r="E47" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B47,"MaskImage.png")</f>
         <v>210003MaskImage.png</v>
       </c>
       <c r="F47" s="2">
@@ -1678,7 +1678,7 @@
         <v>63</v>
       </c>
       <c r="E48" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B48,"MaskImage.png")</f>
         <v>210004MaskImage.png</v>
       </c>
       <c r="F48" s="2">
@@ -1699,7 +1699,7 @@
         <v>64</v>
       </c>
       <c r="E49" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B49,"MaskImage.png")</f>
         <v>210005MaskImage.png</v>
       </c>
       <c r="F49" s="2">
@@ -1720,7 +1720,7 @@
         <v>65</v>
       </c>
       <c r="E50" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B50,"MaskImage.png")</f>
         <v>210006MaskImage.png</v>
       </c>
       <c r="F50" s="2">
@@ -1741,7 +1741,7 @@
         <v>66</v>
       </c>
       <c r="E51" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B51,"MaskImage.png")</f>
         <v>210007MaskImage.png</v>
       </c>
       <c r="F51" s="2">
@@ -1762,7 +1762,7 @@
         <v>67</v>
       </c>
       <c r="E52" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B52,"MaskImage.png")</f>
         <v>210008MaskImage.png</v>
       </c>
       <c r="F52" s="2">
@@ -1783,7 +1783,7 @@
         <v>68</v>
       </c>
       <c r="E53" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B53,"MaskImage.png")</f>
         <v>210009MaskImage.png</v>
       </c>
       <c r="F53" s="2">
@@ -1804,7 +1804,7 @@
         <v>69</v>
       </c>
       <c r="E54" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B54,"MaskImage.png")</f>
         <v>210010MaskImage.png</v>
       </c>
       <c r="F54" s="2">
@@ -1825,7 +1825,7 @@
         <v>70</v>
       </c>
       <c r="E55" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B55,"MaskImage.png")</f>
         <v>210011MaskImage.png</v>
       </c>
       <c r="F55" s="2">
@@ -1846,7 +1846,7 @@
         <v>71</v>
       </c>
       <c r="E56" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B56,"MaskImage.png")</f>
         <v>210012MaskImage.png</v>
       </c>
       <c r="F56" s="2">
@@ -1867,7 +1867,7 @@
         <v>72</v>
       </c>
       <c r="E57" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B57,"MaskImage.png")</f>
         <v>210013MaskImage.png</v>
       </c>
       <c r="F57" s="2">
@@ -1888,7 +1888,7 @@
         <v>73</v>
       </c>
       <c r="E58" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B58,"MaskImage.png")</f>
         <v>210014MaskImage.png</v>
       </c>
       <c r="F58" s="2">
@@ -1909,7 +1909,7 @@
         <v>74</v>
       </c>
       <c r="E59" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE(B59,"MaskImage.png")</f>
         <v>210015MaskImage.png</v>
       </c>
       <c r="F59" s="2">

--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA22A4D-B6ED-4572-84CD-DB7443E21BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81201AFD-D26F-40B9-8F8A-BD4EF26FB558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="2920" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12040" yWindow="1370" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DollCatalogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81201AFD-D26F-40B9-8F8A-BD4EF26FB558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C443794-7DAD-4DEE-8A9F-6F8C01F677DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12040" yWindow="1370" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4810" yWindow="2200" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -92,9 +92,6 @@
     <t>少年剑士</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/Doll/Doll_100001.prefab</t>
-  </si>
-  <si>
     <t>魔法少女</t>
   </si>
   <si>
@@ -258,6 +255,37 @@
   </si>
   <si>
     <t>T-恤</t>
+  </si>
+  <si>
+    <t>isUnlockRandom</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可重复获取</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Doll/DollController_100001.prefab</t>
+  </si>
+  <si>
+    <t>Scale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5,0.5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>vector3#sep=,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放比例</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -622,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -632,10 +660,12 @@
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.4140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="80.58203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="30.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,8 +687,14 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -680,8 +716,14 @@
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -703,8 +745,14 @@
       <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>100001</v>
       </c>
@@ -715,875 +763,1115 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f>CONCATENATE(B4,"MaskImage.png")</f>
+        <f t="shared" ref="E4:E35" si="0">CONCATENATE(B4,"MaskImage.png")</f>
         <v>100001MaskImage.png</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
-        <f t="shared" ref="B5:B43" si="0">B4+1</f>
+        <f t="shared" ref="B5:B43" si="1">B4+1</f>
         <v>100002</v>
       </c>
       <c r="C5" s="3">
         <v>310001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f>CONCATENATE(B5,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100002MaskImage.png</v>
       </c>
       <c r="F5" s="2">
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100003</v>
       </c>
       <c r="C6" s="3">
         <v>310002</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="str">
-        <f>CONCATENATE(B6,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100003MaskImage.png</v>
       </c>
       <c r="F6" s="2">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100004</v>
       </c>
       <c r="C7" s="3">
         <v>310003</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f>CONCATENATE(B7,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100004MaskImage.png</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100005</v>
       </c>
       <c r="C8" s="3">
         <v>310004</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f>CONCATENATE(B8,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100005MaskImage.png</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100006</v>
       </c>
       <c r="C9" s="3">
         <v>310005</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f>CONCATENATE(B9,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100006MaskImage.png</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100007</v>
       </c>
       <c r="C10" s="3">
         <v>310006</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f>CONCATENATE(B10,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100007MaskImage.png</v>
       </c>
       <c r="F10" s="2">
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100008</v>
       </c>
       <c r="C11" s="3">
         <v>310007</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f>CONCATENATE(B11,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100008MaskImage.png</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100009</v>
       </c>
       <c r="C12" s="3">
         <v>310008</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f>CONCATENATE(B12,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100009MaskImage.png</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100010</v>
       </c>
       <c r="C13" s="3">
         <v>310009</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f>CONCATENATE(B13,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100010MaskImage.png</v>
       </c>
       <c r="F13" s="2">
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100011</v>
       </c>
       <c r="C14" s="3">
         <v>310010</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f>CONCATENATE(B14,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100011MaskImage.png</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100012</v>
       </c>
       <c r="C15" s="3">
         <v>310011</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f>CONCATENATE(B15,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100012MaskImage.png</v>
       </c>
       <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100013</v>
       </c>
       <c r="C16" s="3">
         <v>310012</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f>CONCATENATE(B16,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100013MaskImage.png</v>
       </c>
       <c r="F16" s="2">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100014</v>
       </c>
       <c r="C17" s="3">
         <v>310013</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f>CONCATENATE(B17,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100014MaskImage.png</v>
       </c>
       <c r="F17" s="2">
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100015</v>
       </c>
       <c r="C18" s="3">
         <v>310014</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f>CONCATENATE(B18,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100015MaskImage.png</v>
       </c>
       <c r="F18" s="2">
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100016</v>
       </c>
       <c r="C19" s="3">
         <v>310015</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="str">
-        <f>CONCATENATE(B19,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100016MaskImage.png</v>
       </c>
       <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100017</v>
       </c>
       <c r="C20" s="3">
         <v>310016</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f>CONCATENATE(B20,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100017MaskImage.png</v>
       </c>
       <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100018</v>
       </c>
       <c r="C21" s="3">
         <v>310017</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f>CONCATENATE(B21,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100018MaskImage.png</v>
       </c>
       <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100019</v>
       </c>
       <c r="C22" s="3">
         <v>310018</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f>CONCATENATE(B22,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100019MaskImage.png</v>
       </c>
       <c r="F22" s="2">
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100020</v>
       </c>
       <c r="C23" s="3">
         <v>310019</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f>CONCATENATE(B23,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100020MaskImage.png</v>
       </c>
       <c r="F23" s="2">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100021</v>
       </c>
       <c r="C24" s="3">
         <v>310020</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f>CONCATENATE(B24,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100021MaskImage.png</v>
       </c>
       <c r="F24" s="2">
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100022</v>
       </c>
       <c r="C25" s="3">
         <v>310021</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f>CONCATENATE(B25,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100022MaskImage.png</v>
       </c>
       <c r="F25" s="2">
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100023</v>
       </c>
       <c r="C26" s="3">
         <v>310022</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f>CONCATENATE(B26,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100023MaskImage.png</v>
       </c>
       <c r="F26" s="2">
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100024</v>
       </c>
       <c r="C27" s="3">
         <v>310023</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f>CONCATENATE(B27,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100024MaskImage.png</v>
       </c>
       <c r="F27" s="2">
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100025</v>
       </c>
       <c r="C28" s="3">
         <v>310024</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f>CONCATENATE(B28,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100025MaskImage.png</v>
       </c>
       <c r="F28" s="2">
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100026</v>
       </c>
       <c r="C29" s="3">
         <v>310025</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="str">
-        <f>CONCATENATE(B29,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100026MaskImage.png</v>
       </c>
       <c r="F29" s="2">
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100027</v>
       </c>
       <c r="C30" s="3">
         <v>310026</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f>CONCATENATE(B30,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100027MaskImage.png</v>
       </c>
       <c r="F30" s="2">
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100028</v>
       </c>
       <c r="C31" s="3">
         <v>310027</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="str">
-        <f>CONCATENATE(B31,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100028MaskImage.png</v>
       </c>
       <c r="F31" s="2">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100029</v>
       </c>
       <c r="C32" s="3">
         <v>310028</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2" t="str">
-        <f>CONCATENATE(B32,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100029MaskImage.png</v>
       </c>
       <c r="F32" s="2">
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100030</v>
       </c>
       <c r="C33" s="3">
         <v>310029</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="2" t="str">
-        <f>CONCATENATE(B33,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100030MaskImage.png</v>
       </c>
       <c r="F33" s="2">
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100031</v>
       </c>
       <c r="C34" s="3">
         <v>310030</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="2" t="str">
-        <f>CONCATENATE(B34,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100031MaskImage.png</v>
       </c>
       <c r="F34" s="2">
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100032</v>
       </c>
       <c r="C35" s="3">
         <v>310031</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="str">
-        <f>CONCATENATE(B35,"MaskImage.png")</f>
+        <f t="shared" si="0"/>
         <v>100032MaskImage.png</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100033</v>
       </c>
       <c r="C36" s="3">
         <v>310032</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="str">
-        <f>CONCATENATE(B36,"MaskImage.png")</f>
+        <f t="shared" ref="E36:E59" si="2">CONCATENATE(B36,"MaskImage.png")</f>
         <v>100033MaskImage.png</v>
       </c>
       <c r="F36" s="2">
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100034</v>
       </c>
       <c r="C37" s="3">
         <v>310033</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="str">
-        <f>CONCATENATE(B37,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100034MaskImage.png</v>
       </c>
       <c r="F37" s="2">
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100035</v>
       </c>
       <c r="C38" s="3">
         <v>310034</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="str">
-        <f>CONCATENATE(B38,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100035MaskImage.png</v>
       </c>
       <c r="F38" s="2">
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100036</v>
       </c>
       <c r="C39" s="3">
         <v>310035</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="str">
-        <f>CONCATENATE(B39,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100036MaskImage.png</v>
       </c>
       <c r="F39" s="2">
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100037</v>
       </c>
       <c r="C40" s="3">
         <v>310036</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="str">
-        <f>CONCATENATE(B40,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100037MaskImage.png</v>
       </c>
       <c r="F40" s="2">
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100038</v>
       </c>
       <c r="C41" s="3">
         <v>310037</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="2" t="str">
-        <f>CONCATENATE(B41,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100038MaskImage.png</v>
       </c>
       <c r="F41" s="2">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100039</v>
       </c>
       <c r="C42" s="3">
         <v>310038</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E42" s="2" t="str">
-        <f>CONCATENATE(B42,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100039MaskImage.png</v>
       </c>
       <c r="F42" s="2">
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100040</v>
       </c>
       <c r="C43" s="3">
         <v>310039</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="str">
-        <f>CONCATENATE(B43,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>100040MaskImage.png</v>
       </c>
       <c r="F43" s="2">
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>210000</v>
       </c>
@@ -1591,20 +1879,26 @@
         <v>210000</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="str">
-        <f>CONCATENATE(B44,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210000MaskImage.png</v>
       </c>
       <c r="F44" s="2">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>210001</v>
       </c>
@@ -1612,20 +1906,26 @@
         <v>210001</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" s="2" t="str">
-        <f>CONCATENATE(B45,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210001MaskImage.png</v>
       </c>
       <c r="F45" s="2">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>210002</v>
       </c>
@@ -1633,20 +1933,26 @@
         <v>210002</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="str">
-        <f>CONCATENATE(B46,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210002MaskImage.png</v>
       </c>
       <c r="F46" s="2">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>210003</v>
       </c>
@@ -1654,20 +1960,26 @@
         <v>210003</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E47" s="2" t="str">
-        <f>CONCATENATE(B47,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210003MaskImage.png</v>
       </c>
       <c r="F47" s="2">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>210004</v>
       </c>
@@ -1675,20 +1987,26 @@
         <v>210004</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2" t="str">
-        <f>CONCATENATE(B48,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210004MaskImage.png</v>
       </c>
       <c r="F48" s="2">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>210005</v>
       </c>
@@ -1696,20 +2014,26 @@
         <v>210005</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49" s="2" t="str">
-        <f>CONCATENATE(B49,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210005MaskImage.png</v>
       </c>
       <c r="F49" s="2">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>210006</v>
       </c>
@@ -1717,20 +2041,26 @@
         <v>210006</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" s="2" t="str">
-        <f>CONCATENATE(B50,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210006MaskImage.png</v>
       </c>
       <c r="F50" s="2">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>210007</v>
       </c>
@@ -1738,20 +2068,26 @@
         <v>210007</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2" t="str">
-        <f>CONCATENATE(B51,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210007MaskImage.png</v>
       </c>
       <c r="F51" s="2">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>210008</v>
       </c>
@@ -1759,20 +2095,26 @@
         <v>210008</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E52" s="2" t="str">
-        <f>CONCATENATE(B52,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210008MaskImage.png</v>
       </c>
       <c r="F52" s="2">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>210009</v>
       </c>
@@ -1780,20 +2122,26 @@
         <v>210009</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E53" s="2" t="str">
-        <f>CONCATENATE(B53,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210009MaskImage.png</v>
       </c>
       <c r="F53" s="2">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>210010</v>
       </c>
@@ -1801,20 +2149,26 @@
         <v>210010</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2" t="str">
-        <f>CONCATENATE(B54,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210010MaskImage.png</v>
       </c>
       <c r="F54" s="2">
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>210011</v>
       </c>
@@ -1822,20 +2176,26 @@
         <v>210011</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E55" s="2" t="str">
-        <f>CONCATENATE(B55,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210011MaskImage.png</v>
       </c>
       <c r="F55" s="2">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>210012</v>
       </c>
@@ -1843,20 +2203,26 @@
         <v>210012</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" s="2" t="str">
-        <f>CONCATENATE(B56,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210012MaskImage.png</v>
       </c>
       <c r="F56" s="2">
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>210013</v>
       </c>
@@ -1864,20 +2230,26 @@
         <v>210013</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" s="2" t="str">
-        <f>CONCATENATE(B57,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210013MaskImage.png</v>
       </c>
       <c r="F57" s="2">
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>210014</v>
       </c>
@@ -1885,20 +2257,26 @@
         <v>210014</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2" t="str">
-        <f>CONCATENATE(B58,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210014MaskImage.png</v>
       </c>
       <c r="F58" s="2">
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="H58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>210015</v>
       </c>
@@ -1906,17 +2284,23 @@
         <v>210015</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E59" s="2" t="str">
-        <f>CONCATENATE(B59,"MaskImage.png")</f>
+        <f t="shared" si="2"/>
         <v>210015MaskImage.png</v>
       </c>
       <c r="F59" s="2">
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>19</v>
+        <v>77</v>
+      </c>
+      <c r="H59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
